--- a/summary/train_data_before_stand_summary.xlsx
+++ b/summary/train_data_before_stand_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1300</v>
+        <v>7.170888478512505</v>
       </c>
       <c r="C3" t="n">
-        <v>215245</v>
+        <v>12.27953683907434</v>
       </c>
       <c r="D3" t="n">
-        <v>10516.82808219178</v>
+        <v>9.110966323939161</v>
       </c>
       <c r="E3" t="n">
-        <v>9478.5</v>
+        <v>9.156886838722746</v>
       </c>
       <c r="F3" t="n">
-        <v>9981.26493237915</v>
+        <v>0.5173690129860723</v>
       </c>
       <c r="G3" t="n">
-        <v>99625649.65034176</v>
+        <v>0.2676706955981827</v>
       </c>
     </row>
     <row r="4">
@@ -508,19 +508,19 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1600</v>
+        <v>7.378383712996714</v>
       </c>
       <c r="D4" t="n">
-        <v>103.1171232876712</v>
+        <v>2.120263867818605</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>180.7313733581237</v>
+        <v>2.628759342458382</v>
       </c>
       <c r="G4" t="n">
-        <v>32663.82931591351</v>
+        <v>6.910375680562225</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>5644</v>
+        <v>8.638525476583762</v>
       </c>
       <c r="D5" t="n">
-        <v>443.6397260273973</v>
+        <v>4.229730953008728</v>
       </c>
       <c r="E5" t="n">
-        <v>383.5</v>
+        <v>5.951942943437755</v>
       </c>
       <c r="F5" t="n">
-        <v>456.0980908409277</v>
+        <v>2.99205232448562</v>
       </c>
       <c r="G5" t="n">
-        <v>208025.4684687391</v>
+        <v>8.9523771124598</v>
       </c>
     </row>
     <row r="6">
@@ -558,19 +558,19 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1474</v>
+        <v>7.29641326877392</v>
       </c>
       <c r="D6" t="n">
-        <v>46.54931506849315</v>
+        <v>0.6553980425519907</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>161.3192728065417</v>
+        <v>1.845044652452452</v>
       </c>
       <c r="G6" t="n">
-        <v>26023.90777883144</v>
+        <v>3.404189769543387</v>
       </c>
     </row>
     <row r="7">
@@ -583,19 +583,19 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>2336</v>
+        <v>7.756623334538858</v>
       </c>
       <c r="D7" t="n">
-        <v>567.2404109589041</v>
+        <v>5.64837772857256</v>
       </c>
       <c r="E7" t="n">
-        <v>477.5</v>
+        <v>6.170651297395139</v>
       </c>
       <c r="F7" t="n">
-        <v>441.8669552924342</v>
+        <v>1.854020279310137</v>
       </c>
       <c r="G7" t="n">
-        <v>195246.406179406</v>
+        <v>3.43739119609324</v>
       </c>
     </row>
     <row r="8">
@@ -608,19 +608,19 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>6110</v>
+        <v>8.717845704894916</v>
       </c>
       <c r="D8" t="n">
-        <v>1057.429452054794</v>
+        <v>6.750559872941586</v>
       </c>
       <c r="E8" t="n">
-        <v>991.5</v>
+        <v>6.900226885665022</v>
       </c>
       <c r="F8" t="n">
-        <v>438.7053244594708</v>
+        <v>1.145712462400606</v>
       </c>
       <c r="G8" t="n">
-        <v>192462.3617090895</v>
+        <v>1.312657046500059</v>
       </c>
     </row>
     <row r="9">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>334</v>
+        <v>5.814130531825066</v>
       </c>
       <c r="C9" t="n">
-        <v>4692</v>
+        <v>8.453827315794417</v>
       </c>
       <c r="D9" t="n">
-        <v>1162.626712328767</v>
+        <v>7.008452494323159</v>
       </c>
       <c r="E9" t="n">
-        <v>1087</v>
+        <v>6.992096005027085</v>
       </c>
       <c r="F9" t="n">
-        <v>386.5877380410744</v>
+        <v>0.3174311307698364</v>
       </c>
       <c r="G9" t="n">
-        <v>149450.0792037143</v>
+        <v>0.100762522781817</v>
       </c>
     </row>
     <row r="10">
@@ -658,19 +658,19 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2065</v>
+        <v>7.633369649679584</v>
       </c>
       <c r="D10" t="n">
-        <v>346.9924657534247</v>
+        <v>2.864585956701317</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>436.5284358862568</v>
+        <v>3.293311456165734</v>
       </c>
       <c r="G10" t="n">
-        <v>190557.0753373018</v>
+        <v>10.84590034731247</v>
       </c>
     </row>
     <row r="11">
@@ -683,19 +683,19 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>572</v>
+        <v>6.35088571671474</v>
       </c>
       <c r="D11" t="n">
-        <v>5.844520547945206</v>
+        <v>0.09981397635364103</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>48.62308143352019</v>
+        <v>0.7473536208632642</v>
       </c>
       <c r="G11" t="n">
-        <v>2364.204048090736</v>
+        <v>0.5585374346174315</v>
       </c>
     </row>
     <row r="12">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>334</v>
+        <v>5.814130531825066</v>
       </c>
       <c r="C12" t="n">
-        <v>5642</v>
+        <v>8.63817111796914</v>
       </c>
       <c r="D12" t="n">
-        <v>1515.463698630137</v>
+        <v>7.268511760585581</v>
       </c>
       <c r="E12" t="n">
-        <v>1464</v>
+        <v>7.289610521451167</v>
       </c>
       <c r="F12" t="n">
-        <v>525.4803834232025</v>
+        <v>0.3333030092650758</v>
       </c>
       <c r="G12" t="n">
-        <v>276129.6333625959</v>
+        <v>0.1110908959851552</v>
       </c>
     </row>
     <row r="13">
@@ -758,19 +758,19 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1.09861228866811</v>
       </c>
       <c r="D14" t="n">
-        <v>0.05753424657534247</v>
+        <v>0.03948561576858345</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2387526462792118</v>
+        <v>0.1625993297098857</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05700282610532642</v>
+        <v>0.02643854202210413</v>
       </c>
     </row>
     <row r="15">
@@ -858,19 +858,19 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>1.386294361119891</v>
       </c>
       <c r="D18" t="n">
-        <v>1.046575342465753</v>
+        <v>0.7116734676884321</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.6931471805599453</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2203381983840307</v>
+        <v>0.08926775460278703</v>
       </c>
       <c r="G18" t="n">
-        <v>0.04854892166712046</v>
+        <v>0.007968732011823406</v>
       </c>
     </row>
     <row r="19">
@@ -983,19 +983,19 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>857</v>
+        <v>6.754604099487962</v>
       </c>
       <c r="D23" t="n">
-        <v>94.2445205479452</v>
+        <v>2.457206481321175</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>125.3387943517241</v>
+        <v>2.59643457281768</v>
       </c>
       <c r="G23" t="n">
-        <v>15709.81336954378</v>
+        <v>6.74147249092293</v>
       </c>
     </row>
     <row r="24">
@@ -1008,19 +1008,19 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>547</v>
+        <v>6.306275286948016</v>
       </c>
       <c r="D24" t="n">
-        <v>46.66027397260274</v>
+        <v>2.30854083307069</v>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>3.258096538021482</v>
       </c>
       <c r="F24" t="n">
-        <v>66.25602767664971</v>
+        <v>2.152387338153984</v>
       </c>
       <c r="G24" t="n">
-        <v>4389.861203488972</v>
+        <v>4.63277125344559</v>
       </c>
     </row>
     <row r="25">
@@ -1033,19 +1033,19 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>552</v>
+        <v>6.315358001522335</v>
       </c>
       <c r="D25" t="n">
-        <v>21.9541095890411</v>
+        <v>0.6980186967122098</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>61.1191486017286</v>
+        <v>1.727316924495865</v>
       </c>
       <c r="G25" t="n">
-        <v>3735.550325800183</v>
+        <v>2.983623757649855</v>
       </c>
     </row>
     <row r="26">
@@ -1058,19 +1058,19 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>508</v>
+        <v>6.232448016550522</v>
       </c>
       <c r="D26" t="n">
-        <v>3.40958904109589</v>
+        <v>0.08567852983026086</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>29.31733055678188</v>
+        <v>0.6668762442874228</v>
       </c>
       <c r="G26" t="n">
-        <v>859.5058709756165</v>
+        <v>0.4447239251948983</v>
       </c>
     </row>
     <row r="27">
@@ -1083,19 +1083,19 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>480</v>
+        <v>6.175867270105761</v>
       </c>
       <c r="D27" t="n">
-        <v>15.06095890410959</v>
+        <v>0.4106714853662551</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>55.75741528187417</v>
+        <v>1.403193680424342</v>
       </c>
       <c r="G27" t="n">
-        <v>3108.889358915376</v>
+        <v>1.96895250478281</v>
       </c>
     </row>
     <row r="28">
@@ -1108,19 +1108,19 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>738</v>
+        <v>6.605297920948201</v>
       </c>
       <c r="D28" t="n">
-        <v>2.758904109589041</v>
+        <v>0.03043103638716643</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>40.17730694453019</v>
+        <v>0.4386846995436171</v>
       </c>
       <c r="G28" t="n">
-        <v>1614.215993314994</v>
+        <v>0.1924442656136736</v>
       </c>
     </row>
     <row r="29">
@@ -1133,19 +1133,19 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>15500</v>
+        <v>9.648659816955295</v>
       </c>
       <c r="D29" t="n">
-        <v>43.48904109589041</v>
+        <v>0.2334559358062459</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>496.1230244579442</v>
+        <v>1.226029613513928</v>
       </c>
       <c r="G29" t="n">
-        <v>246138.0553972978</v>
+        <v>1.503148613213111</v>
       </c>
     </row>
     <row r="30">
@@ -1246,6 +1246,181 @@
       </c>
       <c r="G33" t="n">
         <v>1.763836649234323</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TotalArea</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>5.814130531825066</v>
+      </c>
+      <c r="C34" t="n">
+        <v>9.371863806132854</v>
+      </c>
+      <c r="D34" t="n">
+        <v>7.805225121037318</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7.816013757863496</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.3130940101379205</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.09802785918424428</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TotalBaths</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.210616438356164</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.7853985534332735</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.6168508877350786</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TotalPorchArea</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>6.93537044601511</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4.249517648970637</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5.10594547390058</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.07533554294215</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4.307017615798989</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AvgRoomSize</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4.795790545596741</v>
+      </c>
+      <c r="C37" t="n">
+        <v>6.155211888465535</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5.428463700514915</v>
+      </c>
+      <c r="E37" t="n">
+        <v>5.427150238391005</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.1881898947016057</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.03541543646780143</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LotUtilization</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.009414532481816243</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.665459703220337</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.1621324980635483</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.1446952173778887</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.08516006528933652</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.007252236720084058</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Qual_x_Area</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5.814130531825066</v>
+      </c>
+      <c r="C39" t="n">
+        <v>10.94059670861019</v>
+      </c>
+      <c r="D39" t="n">
+        <v>9.048695068258059</v>
+      </c>
+      <c r="E39" t="n">
+        <v>9.084890521258767</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.5159593830869516</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.2662140849954676</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TotalQualCond</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="n">
+        <v>19</v>
+      </c>
+      <c r="D40" t="n">
+        <v>11.67465753424658</v>
+      </c>
+      <c r="E40" t="n">
+        <v>12</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.693527234910995</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.86803449538528</v>
       </c>
     </row>
   </sheetData>

--- a/summary/train_data_before_stand_summary.xlsx
+++ b/summary/train_data_before_stand_summary.xlsx
@@ -461,16 +461,16 @@
         <v>313</v>
       </c>
       <c r="D2" t="n">
-        <v>57.62328767123287</v>
+        <v>57.77482876712329</v>
       </c>
       <c r="E2" t="n">
         <v>63</v>
       </c>
       <c r="F2" t="n">
-        <v>34.66430423090888</v>
+        <v>34.90690004743777</v>
       </c>
       <c r="G2" t="n">
-        <v>1201.613987813007</v>
+        <v>1218.491670921811</v>
       </c>
     </row>
     <row r="3">
@@ -486,16 +486,16 @@
         <v>12.27953683907434</v>
       </c>
       <c r="D3" t="n">
-        <v>9.110966323939161</v>
+        <v>9.112450742546844</v>
       </c>
       <c r="E3" t="n">
-        <v>9.156886838722746</v>
+        <v>9.15915233520675</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5173690129860723</v>
+        <v>0.529879548733956</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2676706955981827</v>
+        <v>0.2807723361665009</v>
       </c>
     </row>
     <row r="4">
@@ -511,16 +511,16 @@
         <v>7.378383712996714</v>
       </c>
       <c r="D4" t="n">
-        <v>2.120263867818605</v>
+        <v>2.154126531299229</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2.628759342458382</v>
+        <v>2.647213621788636</v>
       </c>
       <c r="G4" t="n">
-        <v>6.910375680562225</v>
+        <v>7.007739959383306</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         <v>8.638525476583762</v>
       </c>
       <c r="D5" t="n">
-        <v>4.229730953008728</v>
+        <v>4.17710515673616</v>
       </c>
       <c r="E5" t="n">
-        <v>5.951942943437755</v>
+        <v>5.928257584680153</v>
       </c>
       <c r="F5" t="n">
-        <v>2.99205232448562</v>
+        <v>3.011575560389864</v>
       </c>
       <c r="G5" t="n">
-        <v>8.9523771124598</v>
+        <v>9.06958735593752</v>
       </c>
     </row>
     <row r="6">
@@ -561,16 +561,16 @@
         <v>7.29641326877392</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6553980425519907</v>
+        <v>0.6379329067870181</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.845044652452452</v>
+        <v>1.823592465096285</v>
       </c>
       <c r="G6" t="n">
-        <v>3.404189769543387</v>
+        <v>3.325489478755947</v>
       </c>
     </row>
     <row r="7">
@@ -586,16 +586,16 @@
         <v>7.756623334538858</v>
       </c>
       <c r="D7" t="n">
-        <v>5.64837772857256</v>
+        <v>5.663348011711871</v>
       </c>
       <c r="E7" t="n">
-        <v>6.170651297395139</v>
+        <v>6.186208623900494</v>
       </c>
       <c r="F7" t="n">
-        <v>1.854020279310137</v>
+        <v>1.850594145829385</v>
       </c>
       <c r="G7" t="n">
-        <v>3.43739119609324</v>
+        <v>3.424698692577992</v>
       </c>
     </row>
     <row r="8">
@@ -611,16 +611,16 @@
         <v>8.717845704894916</v>
       </c>
       <c r="D8" t="n">
-        <v>6.750559872941586</v>
+        <v>6.749780358135241</v>
       </c>
       <c r="E8" t="n">
-        <v>6.900226885665022</v>
+        <v>6.898714534329988</v>
       </c>
       <c r="F8" t="n">
-        <v>1.145712462400606</v>
+        <v>1.153291746145229</v>
       </c>
       <c r="G8" t="n">
-        <v>1.312657046500059</v>
+        <v>1.330081851726713</v>
       </c>
     </row>
     <row r="9">
@@ -636,16 +636,16 @@
         <v>8.453827315794417</v>
       </c>
       <c r="D9" t="n">
-        <v>7.008452494323159</v>
+        <v>7.008283073189277</v>
       </c>
       <c r="E9" t="n">
-        <v>6.992096005027085</v>
+        <v>6.99301512293296</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3174311307698364</v>
+        <v>0.3187007630385142</v>
       </c>
       <c r="G9" t="n">
-        <v>0.100762522781817</v>
+        <v>0.1015701763613312</v>
       </c>
     </row>
     <row r="10">
@@ -661,16 +661,16 @@
         <v>7.633369649679584</v>
       </c>
       <c r="D10" t="n">
-        <v>2.864585956701317</v>
+        <v>2.914345674023636</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>3.293311456165734</v>
+        <v>3.303388225221221</v>
       </c>
       <c r="G10" t="n">
-        <v>10.84590034731247</v>
+        <v>10.91237376653021</v>
       </c>
     </row>
     <row r="11">
@@ -686,16 +686,16 @@
         <v>6.35088571671474</v>
       </c>
       <c r="D11" t="n">
-        <v>0.09981397635364103</v>
+        <v>0.09615364717808898</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7473536208632642</v>
+        <v>0.7351753033944782</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5585374346174315</v>
+        <v>0.540482726721163</v>
       </c>
     </row>
     <row r="12">
@@ -711,16 +711,16 @@
         <v>8.63817111796914</v>
       </c>
       <c r="D12" t="n">
-        <v>7.268511760585581</v>
+        <v>7.272919846475015</v>
       </c>
       <c r="E12" t="n">
-        <v>7.289610521451167</v>
+        <v>7.290974778142981</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3333030092650758</v>
+        <v>0.3370545265483014</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1110908959851552</v>
+        <v>0.1136057538666996</v>
       </c>
     </row>
     <row r="13">
@@ -736,16 +736,16 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4253424657534247</v>
+        <v>0.4118150684931507</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5189106060898065</v>
+        <v>0.5194725359023397</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2692682171124903</v>
+        <v>0.2698517155568076</v>
       </c>
     </row>
     <row r="14">
@@ -761,16 +761,16 @@
         <v>1.09861228866811</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03948561576858345</v>
+        <v>0.04282909249655175</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1625993297098857</v>
+        <v>0.1692330020483432</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02643854202210413</v>
+        <v>0.02863980898229455</v>
       </c>
     </row>
     <row r="15">
@@ -786,16 +786,16 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>1.565068493150685</v>
+        <v>1.574486301369863</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5509158012954317</v>
+        <v>0.5565837864870933</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3035082201169876</v>
+        <v>0.3097855113803102</v>
       </c>
     </row>
     <row r="16">
@@ -811,16 +811,16 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3828767123287671</v>
+        <v>0.3895547945205479</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5028853810928914</v>
+        <v>0.5034181095801548</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2528937065169427</v>
+        <v>0.2534297930532567</v>
       </c>
     </row>
     <row r="17">
@@ -836,16 +836,16 @@
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>2.866438356164383</v>
+        <v>2.875</v>
       </c>
       <c r="E17" t="n">
         <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8157780441442284</v>
+        <v>0.8184619931773992</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6654938173077826</v>
+        <v>0.6698800342759211</v>
       </c>
     </row>
     <row r="18">
@@ -861,16 +861,16 @@
         <v>1.386294361119891</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7116734676884321</v>
+        <v>0.7101572749925652</v>
       </c>
       <c r="E18" t="n">
         <v>0.6931471805599453</v>
       </c>
       <c r="F18" t="n">
-        <v>0.08926775460278703</v>
+        <v>0.08623640202770881</v>
       </c>
       <c r="G18" t="n">
-        <v>0.007968732011823406</v>
+        <v>0.00743671703468462</v>
       </c>
     </row>
     <row r="19">
@@ -886,16 +886,16 @@
         <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>6.517808219178082</v>
+        <v>6.537671232876712</v>
       </c>
       <c r="E19" t="n">
         <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>1.62539329058405</v>
+        <v>1.628353757747806</v>
       </c>
       <c r="G19" t="n">
-        <v>2.641903349075647</v>
+        <v>2.651535960371401</v>
       </c>
     </row>
     <row r="20">
@@ -911,16 +911,16 @@
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>0.613013698630137</v>
+        <v>0.6164383561643836</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6446663863122295</v>
+        <v>0.6320247950252325</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4155947496408687</v>
+        <v>0.3994553415266871</v>
       </c>
     </row>
     <row r="21">
@@ -936,16 +936,16 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.767123287671233</v>
+        <v>1.782534246575342</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7473150101111095</v>
+        <v>0.7570087815295705</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5584797243373676</v>
+        <v>0.5730622953128851</v>
       </c>
     </row>
     <row r="22">
@@ -961,16 +961,16 @@
         <v>1418</v>
       </c>
       <c r="D22" t="n">
-        <v>472.9801369863014</v>
+        <v>476.9905821917808</v>
       </c>
       <c r="E22" t="n">
-        <v>480</v>
+        <v>479.5</v>
       </c>
       <c r="F22" t="n">
-        <v>213.8048414533804</v>
+        <v>216.955851234977</v>
       </c>
       <c r="G22" t="n">
-        <v>45712.51022890514</v>
+        <v>47069.8413850935</v>
       </c>
     </row>
     <row r="23">
@@ -986,16 +986,16 @@
         <v>6.754604099487962</v>
       </c>
       <c r="D23" t="n">
-        <v>2.457206481321175</v>
+        <v>2.436359291963893</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>2.59643457281768</v>
+        <v>2.593976530829156</v>
       </c>
       <c r="G23" t="n">
-        <v>6.74147249092293</v>
+        <v>6.728714242492464</v>
       </c>
     </row>
     <row r="24">
@@ -1011,16 +1011,16 @@
         <v>6.306275286948016</v>
       </c>
       <c r="D24" t="n">
-        <v>2.30854083307069</v>
+        <v>2.35446747432967</v>
       </c>
       <c r="E24" t="n">
-        <v>3.258096538021482</v>
+        <v>3.295836866004329</v>
       </c>
       <c r="F24" t="n">
-        <v>2.152387338153984</v>
+        <v>2.150861518111726</v>
       </c>
       <c r="G24" t="n">
-        <v>4.63277125344559</v>
+        <v>4.62620527009388</v>
       </c>
     </row>
     <row r="25">
@@ -1036,16 +1036,16 @@
         <v>6.315358001522335</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6980186967122098</v>
+        <v>0.693985809667263</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1.727316924495865</v>
+        <v>1.726272853523365</v>
       </c>
       <c r="G25" t="n">
-        <v>2.983623757649855</v>
+        <v>2.9800179648117</v>
       </c>
     </row>
     <row r="26">
@@ -1061,16 +1061,16 @@
         <v>6.232448016550522</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08567852983026086</v>
+        <v>0.08451007627695135</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6668762442874228</v>
+        <v>0.6620642035379279</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4447239251948983</v>
+        <v>0.4383290096063109</v>
       </c>
     </row>
     <row r="27">
@@ -1086,16 +1086,16 @@
         <v>6.175867270105761</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4106714853662551</v>
+        <v>0.3982792704148409</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1.403193680424342</v>
+        <v>1.384070897750644</v>
       </c>
       <c r="G27" t="n">
-        <v>1.96895250478281</v>
+        <v>1.915652250000273</v>
       </c>
     </row>
     <row r="28">
@@ -1111,16 +1111,16 @@
         <v>6.605297920948201</v>
       </c>
       <c r="D28" t="n">
-        <v>0.03043103638716643</v>
+        <v>0.03803879548395803</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4386846995436171</v>
+        <v>0.4902110977170798</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1924442656136736</v>
+        <v>0.2403069203249844</v>
       </c>
     </row>
     <row r="29">
@@ -1136,16 +1136,16 @@
         <v>9.648659816955295</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2334559358062459</v>
+        <v>0.1823360088525793</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1.226029613513928</v>
+        <v>1.096084664199043</v>
       </c>
       <c r="G29" t="n">
-        <v>1.503148613213111</v>
+        <v>1.20140159109233</v>
       </c>
     </row>
     <row r="30">
@@ -1161,16 +1161,16 @@
         <v>136</v>
       </c>
       <c r="D30" t="n">
-        <v>36.54794520547945</v>
+        <v>35.6583904109589</v>
       </c>
       <c r="E30" t="n">
-        <v>35</v>
+        <v>33.5</v>
       </c>
       <c r="F30" t="n">
-        <v>30.25015244565461</v>
+        <v>30.2339449809685</v>
       </c>
       <c r="G30" t="n">
-        <v>915.0717229853437</v>
+        <v>914.0914291122301</v>
       </c>
     </row>
     <row r="31">
@@ -1183,19 +1183,19 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D31" t="n">
-        <v>22.95068493150685</v>
+        <v>22.36986301369863</v>
       </c>
       <c r="E31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F31" t="n">
-        <v>20.6398745240066</v>
+        <v>20.61754851872774</v>
       </c>
       <c r="G31" t="n">
-        <v>426.0044203667365</v>
+        <v>425.0833069220926</v>
       </c>
     </row>
     <row r="32">
@@ -1211,16 +1211,16 @@
         <v>107</v>
       </c>
       <c r="D32" t="n">
-        <v>27.68013698630137</v>
+        <v>27.00256849315069</v>
       </c>
       <c r="E32" t="n">
-        <v>23.5</v>
+        <v>21</v>
       </c>
       <c r="F32" t="n">
-        <v>24.9501438990715</v>
+        <v>25.01209634168553</v>
       </c>
       <c r="G32" t="n">
-        <v>622.5096805843748</v>
+        <v>625.6049634057589</v>
       </c>
     </row>
     <row r="33">
@@ -1233,19 +1233,19 @@
         <v>2006</v>
       </c>
       <c r="C33" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D33" t="n">
-        <v>2007.815753424657</v>
+        <v>2007.369863013699</v>
       </c>
       <c r="E33" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="F33" t="n">
-        <v>1.32809512055211</v>
+        <v>1.072448119195144</v>
       </c>
       <c r="G33" t="n">
-        <v>1.763836649234323</v>
+        <v>1.150144968365203</v>
       </c>
     </row>
     <row r="34">
@@ -1261,16 +1261,16 @@
         <v>9.371863806132854</v>
       </c>
       <c r="D34" t="n">
-        <v>7.805225121037318</v>
+        <v>7.807891136283952</v>
       </c>
       <c r="E34" t="n">
-        <v>7.816013757863496</v>
+        <v>7.820037908814887</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3130940101379205</v>
+        <v>0.3179325259103387</v>
       </c>
       <c r="G34" t="n">
-        <v>0.09802785918424428</v>
+        <v>0.1010810910317282</v>
       </c>
     </row>
     <row r="35">
@@ -1286,16 +1286,16 @@
         <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>2.210616438356164</v>
+        <v>2.212328767123288</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7853985534332735</v>
+        <v>0.7908227174802185</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6168508877350786</v>
+        <v>0.6254005704827975</v>
       </c>
     </row>
     <row r="36">
@@ -1311,16 +1311,16 @@
         <v>6.93537044601511</v>
       </c>
       <c r="D36" t="n">
-        <v>4.249517648970637</v>
+        <v>4.236598415559105</v>
       </c>
       <c r="E36" t="n">
-        <v>5.10594547390058</v>
+        <v>5.099866427824199</v>
       </c>
       <c r="F36" t="n">
-        <v>2.07533554294215</v>
+        <v>2.086136216567057</v>
       </c>
       <c r="G36" t="n">
-        <v>4.307017615798989</v>
+        <v>4.351964314072714</v>
       </c>
     </row>
     <row r="37">
@@ -1336,16 +1336,16 @@
         <v>6.155211888465535</v>
       </c>
       <c r="D37" t="n">
-        <v>5.428463700514915</v>
+        <v>5.4300920902481</v>
       </c>
       <c r="E37" t="n">
-        <v>5.427150238391005</v>
+        <v>5.429345628954441</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1881898947016057</v>
+        <v>0.1887018080214743</v>
       </c>
       <c r="G37" t="n">
-        <v>0.03541543646780143</v>
+        <v>0.03560837235057335</v>
       </c>
     </row>
     <row r="38">
@@ -1361,16 +1361,16 @@
         <v>0.665459703220337</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1621324980635483</v>
+        <v>0.163002925769128</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1446952173778887</v>
+        <v>0.1436564464782009</v>
       </c>
       <c r="F38" t="n">
-        <v>0.08516006528933652</v>
+        <v>0.08669013040835735</v>
       </c>
       <c r="G38" t="n">
-        <v>0.007252236720084058</v>
+        <v>0.007515178710218005</v>
       </c>
     </row>
     <row r="39">
@@ -1386,16 +1386,16 @@
         <v>10.94059670861019</v>
       </c>
       <c r="D39" t="n">
-        <v>9.048695068258059</v>
+        <v>9.056736946355361</v>
       </c>
       <c r="E39" t="n">
-        <v>9.084890521258767</v>
+        <v>9.090993385817479</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5159593830869516</v>
+        <v>0.5236865112848812</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2662140849954676</v>
+        <v>0.27424756210173</v>
       </c>
     </row>
     <row r="40">
@@ -1411,16 +1411,16 @@
         <v>19</v>
       </c>
       <c r="D40" t="n">
-        <v>11.67465753424658</v>
+        <v>11.69006849315068</v>
       </c>
       <c r="E40" t="n">
         <v>12</v>
       </c>
       <c r="F40" t="n">
-        <v>1.693527234910995</v>
+        <v>1.682055296656923</v>
       </c>
       <c r="G40" t="n">
-        <v>2.86803449538528</v>
+        <v>2.829310021011609</v>
       </c>
     </row>
   </sheetData>
